--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_338_R34.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_338_R34.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3942</v>
+        <v>0.9401</v>
       </c>
       <c r="E2" t="n">
-        <v>2.8793</v>
+        <v>3.1899</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.4851</v>
+        <v>-2.2498</v>
       </c>
       <c r="G2" t="n">
         <v>-0.665</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.4589</v>
+        <v>-0.9131</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.731</v>
+        <v>-0.4204</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7279</v>
+        <v>-0.4927</v>
       </c>
       <c r="V2" t="n">
         <v>2.2862</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>B. COLSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1683</v>
+        <v>-0.4653</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6483</v>
+        <v>0.4439</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.8166</v>
+        <v>-0.9092</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.5307</v>
+        <v>-0.669</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6808</v>
+        <v>-0.6421</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8499</v>
+        <v>-0.0269</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0386</v>
+        <v>0.9467</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.4265</v>
+        <v>-0.8165</v>
       </c>
       <c r="L3" t="n">
-        <v>0.465</v>
+        <v>1.7631</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5692</v>
+        <v>-1.6156</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2543</v>
+        <v>0.1744</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.3149</v>
+        <v>-1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>0.9278</v>
+        <v>2.5515</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0876</v>
+        <v>2.7834</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5068</v>
+        <v>-0.2034</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7695</v>
+        <v>-0.2708</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2627</v>
+        <v>0.0674</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. SILVA</t>
+          <t>K. BIRCH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2301</v>
+        <v>-0.5524</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7604</v>
+        <v>-1.0819</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.9905</v>
+        <v>0.5295</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3824</v>
+        <v>-1.8692</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6459</v>
+        <v>-1.2268</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7365</v>
+        <v>-0.6424</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4131</v>
+        <v>-0.5215</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.4131</v>
+        <v>-0.6687</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1472</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9692</v>
+        <v>-1.3477</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2327</v>
+        <v>-0.5581</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7365</v>
+        <v>-0.7896</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.007900000000000001</v>
+        <v>0.4817</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1889</v>
+        <v>0.4602</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.181</v>
+        <v>0.0215</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1444</v>
+        <v>-0.7886</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>-0.7886</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. JANTUNEN</t>
+          <t>C. SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.457</v>
+        <v>-0.7019</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8554</v>
+        <v>0.2886</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3984</v>
+        <v>-0.9905</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.1106</v>
+        <v>-2.3824</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1427</v>
+        <v>-0.6459</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9679</v>
+        <v>-1.7365</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.2978</v>
+        <v>-0.4131</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0133</v>
+        <v>-0.4131</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2845</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.8127</v>
+        <v>-1.9692</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1294</v>
+        <v>-0.2327</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6834</v>
+        <v>-1.7365</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>1.1896</v>
+        <v>-0.4639</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4604</v>
+        <v>-0.2829</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7292</v>
+        <v>-0.181</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5361</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1418</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. COLSON</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.5242</v>
+        <v>-1.0282</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0153</v>
+        <v>-0.4133</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5395</v>
+        <v>-0.6149</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.669</v>
+        <v>-1.5307</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6421</v>
+        <v>-0.6808</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0269</v>
+        <v>-0.8499</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9467</v>
+        <v>0.0386</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8165</v>
+        <v>-0.4265</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7631</v>
+        <v>0.465</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6156</v>
+        <v>-1.5692</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1744</v>
+        <v>-0.2543</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.79</v>
+        <v>-1.3149</v>
       </c>
       <c r="P6" t="n">
-        <v>2.5515</v>
+        <v>0.9278</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7834</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2623</v>
+        <v>0.6469</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6994</v>
+        <v>0.7079</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4371</v>
+        <v>-0.0611</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.1444</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. BIRCH</t>
+          <t>M. JANTUNEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6361</v>
+        <v>-1.2575</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.964</v>
+        <v>-1.2526</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3278</v>
+        <v>-0.0049</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.8692</v>
+        <v>-3.1106</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2268</v>
+        <v>-0.1427</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6424</v>
+        <v>-2.9679</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5215</v>
+        <v>-0.2978</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.6687</v>
+        <v>-0.0133</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1472</v>
+        <v>-0.2845</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3477</v>
+        <v>-2.8127</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5581</v>
+        <v>-0.1294</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7896</v>
+        <v>-2.6834</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.232</v>
+        <v>-1.1598</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S7" t="n">
-        <v>0.398</v>
+        <v>0.3892</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.0633</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1801</v>
+        <v>0.326</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7886</v>
+        <v>0.1418</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4736</v>
+        <v>-1.2714</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0617</v>
+        <v>0.1742</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.412</v>
+        <v>-1.4456</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2575</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8087</v>
+        <v>-0.6065</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4353</v>
+        <v>-0.4689</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5671</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. BITIM</t>
+          <t>N. DE COLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5521</v>
+        <v>-1.2797</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4971</v>
+        <v>0.2576</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.0493</v>
+        <v>-1.5373</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4771</v>
+        <v>0.4026</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1021</v>
+        <v>-0.0491</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5792</v>
+        <v>0.4517</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6385999999999999</v>
+        <v>2.2896</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6385999999999999</v>
+        <v>0.2051</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.0844</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1157</v>
+        <v>-1.887</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5365</v>
+        <v>-0.2543</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.5792</v>
+        <v>-1.6327</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3971</v>
+        <v>-0.9711</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1415</v>
+        <v>-0.161</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2557</v>
+        <v>-0.8101</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>N. DE COLO</t>
+          <t>O. BITIM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9771</v>
+        <v>-1.4775</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1709</v>
+        <v>0.5718</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8062</v>
+        <v>-2.0493</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4026</v>
+        <v>-1.4771</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0491</v>
+        <v>0.1021</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4517</v>
+        <v>-1.5792</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2896</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2051</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>2.0844</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.887</v>
+        <v>-2.1157</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2543</v>
+        <v>-0.5365</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.6327</v>
+        <v>-1.5792</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.3195</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6685</v>
+        <v>-0.3224</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5895</v>
+        <v>-0.0668</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0789</v>
+        <v>-0.2557</v>
       </c>
       <c r="V10" t="n">
-        <v>1.6083</v>
+        <v>-0.1418</v>
       </c>
       <c r="W10" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.3688</v>
+        <v>-2.526</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8817</v>
+        <v>-2.9381</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5129</v>
+        <v>0.4121</v>
       </c>
       <c r="G11" t="n">
         <v>-0.6261</v>
@@ -1312,13 +1312,13 @@
         <v>2.7834</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1602</v>
+        <v>-0.3174</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.187</v>
+        <v>-0.2434</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0268</v>
+        <v>-0.074</v>
       </c>
       <c r="V11" t="n">
         <v>0.5051</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.9931</v>
+        <v>-9.6198</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1333</v>
+        <v>-0.7598999999999996</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.860100000000001</v>
+        <v>-8.8599</v>
       </c>
       <c r="G12" t="n">
         <v>-13.185</v>
@@ -1381,7 +1381,7 @@
         <v>-17.6324</v>
       </c>
       <c r="P12" t="n">
-        <v>3.4794</v>
+        <v>3.479399999999999</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.9174</v>
@@ -1390,16 +1390,16 @@
         <v>17.3965</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.6534</v>
+        <v>-2.28</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7249000000000002</v>
+        <v>-0.3514</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.9285</v>
+        <v>-1.9286</v>
       </c>
       <c r="V12" t="n">
-        <v>2.366000000000001</v>
+        <v>2.366</v>
       </c>
       <c r="W12" t="n">
         <v>6.4643</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.7072</v>
+        <v>5.602</v>
       </c>
       <c r="E13" t="n">
-        <v>3.5559</v>
+        <v>3.6738</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1514</v>
+        <v>1.9282</v>
       </c>
       <c r="G13" t="n">
         <v>2.7478</v>
@@ -1468,13 +1468,13 @@
         <v>2.3195</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4982</v>
+        <v>0.393</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6827</v>
+        <v>0.4595</v>
       </c>
       <c r="V13" t="n">
         <v>0.1418</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.0354</v>
+        <v>2.6925</v>
       </c>
       <c r="E14" t="n">
-        <v>3.4312</v>
+        <v>2.114</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.3958</v>
+        <v>0.5785</v>
       </c>
       <c r="G14" t="n">
-        <v>2.4258</v>
+        <v>5.186</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.7962</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5291</v>
+        <v>4.3898</v>
       </c>
       <c r="J14" t="n">
-        <v>2.7942</v>
+        <v>6.1622</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5797</v>
+        <v>1.294</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2146</v>
+        <v>4.8682</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3684</v>
+        <v>-0.9761</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6830000000000001</v>
+        <v>-0.4978</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3145</v>
+        <v>-0.4783</v>
       </c>
       <c r="P14" t="n">
-        <v>0.232</v>
+        <v>-3.2473</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.232</v>
+        <v>-6.0307</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4639</v>
+        <v>2.7834</v>
       </c>
       <c r="S14" t="n">
-        <v>0.9137</v>
+        <v>-0.0659</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8689</v>
+        <v>0.0907</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0448</v>
+        <v>-0.1566</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5361</v>
+        <v>0.8197</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.8919</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.4046</v>
+        <v>2.6308</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9887</v>
+        <v>2.9594</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4159</v>
+        <v>-0.3286</v>
       </c>
       <c r="G15" t="n">
-        <v>3.587</v>
+        <v>2.4258</v>
       </c>
       <c r="H15" t="n">
-        <v>4.5808</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9937</v>
+        <v>1.5291</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5085</v>
+        <v>2.7942</v>
       </c>
       <c r="K15" t="n">
-        <v>4.1844</v>
+        <v>1.5797</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.6758999999999999</v>
+        <v>1.2146</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0785</v>
+        <v>-0.3684</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3963</v>
+        <v>-0.6830000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.3178</v>
+        <v>0.3145</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.9278</v>
+        <v>0.232</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.3195</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>0.4639</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1129</v>
+        <v>0.5091</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2636</v>
+        <v>0.3971</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3765</v>
+        <v>0.112</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>-0.5361</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8794999999999999</v>
+        <v>2.2137</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0525</v>
+        <v>1.5169</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.173</v>
+        <v>0.6968</v>
       </c>
       <c r="G16" t="n">
-        <v>5.186</v>
+        <v>3.587</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7962</v>
+        <v>4.5808</v>
       </c>
       <c r="I16" t="n">
-        <v>4.3898</v>
+        <v>-0.9937</v>
       </c>
       <c r="J16" t="n">
-        <v>6.1622</v>
+        <v>3.5085</v>
       </c>
       <c r="K16" t="n">
-        <v>1.294</v>
+        <v>4.1844</v>
       </c>
       <c r="L16" t="n">
-        <v>4.8682</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.9761</v>
+        <v>0.0785</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4978</v>
+        <v>0.3963</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4783</v>
+        <v>-0.3178</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.2473</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q16" t="n">
-        <v>-6.0307</v>
+        <v>-2.3195</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7834</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.8789</v>
+        <v>-0.3038</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9709</v>
+        <v>-0.2082</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.908</v>
+        <v>-0.0955</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8197</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.8919</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7819</v>
+        <v>0.9842</v>
       </c>
       <c r="E17" t="n">
-        <v>0.302</v>
+        <v>0.5379</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4799</v>
+        <v>0.4463</v>
       </c>
       <c r="G17" t="n">
         <v>1.3278</v>
@@ -1780,13 +1780,13 @@
         <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0303</v>
+        <v>0.172</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0668</v>
+        <v>0.1691</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0365</v>
+        <v>0.0029</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2836</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6985</v>
+        <v>0.8335</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4968</v>
+        <v>0.7327</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2017</v>
+        <v>0.1008</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1387</v>
@@ -1858,13 +1858,13 @@
         <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4635</v>
+        <v>0.5985</v>
       </c>
       <c r="T18" t="n">
-        <v>0.1573</v>
+        <v>0.3932</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V18" t="n">
         <v>0.1418</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.68</v>
+        <v>0.3496</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8352000000000001</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1552</v>
+        <v>-0.3676</v>
       </c>
       <c r="G19" t="n">
         <v>2.128</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>1.6601</v>
+        <v>1.3298</v>
       </c>
       <c r="T19" t="n">
-        <v>0.9085</v>
+        <v>0.7905</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7517</v>
+        <v>0.5392</v>
       </c>
       <c r="V19" t="n">
         <v>-0.7886</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0769</v>
+        <v>0.3065</v>
       </c>
       <c r="E20" t="n">
-        <v>1.5755</v>
+        <v>1.2216</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4986</v>
+        <v>-0.9152</v>
       </c>
       <c r="G20" t="n">
         <v>2.4851</v>
@@ -2014,13 +2014,13 @@
         <v>1.1598</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5017</v>
+        <v>0.7312</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7591</v>
+        <v>0.4052</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2574</v>
+        <v>0.326</v>
       </c>
       <c r="V20" t="n">
         <v>-1.7501</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5518</v>
+        <v>-0.2151</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0128</v>
+        <v>0.2231</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.539</v>
+        <v>-0.4382</v>
       </c>
       <c r="G21" t="n">
         <v>-0.6349</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8448</v>
+        <v>-0.5081</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1726</v>
+        <v>-0.0718</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4797</v>
+        <v>-1.5812</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8221</v>
+        <v>-2.058</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3423</v>
+        <v>0.4768</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2889</v>
@@ -2170,13 +2170,13 @@
         <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5772</v>
+        <v>0.4758</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4129</v>
+        <v>0.177</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1643</v>
+        <v>0.2987</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.2392</v>
+        <v>-2.2507</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.543</v>
+        <v>-2.7789</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3037</v>
+        <v>0.5282</v>
       </c>
       <c r="G23" t="n">
         <v>-3.64</v>
@@ -2248,13 +2248,13 @@
         <v>1.6237</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9058</v>
+        <v>0.8944</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4525</v>
+        <v>0.2166</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4534</v>
+        <v>0.6778</v>
       </c>
       <c r="V23" t="n">
         <v>0.031</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>9.993299999999998</v>
+        <v>11.5658</v>
       </c>
       <c r="E24" t="n">
-        <v>8.8599</v>
+        <v>8.8597</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1333</v>
+        <v>2.706</v>
       </c>
       <c r="G24" t="n">
         <v>13.185</v>
@@ -2302,7 +2302,7 @@
         <v>20.2294</v>
       </c>
       <c r="K24" t="n">
-        <v>2.5969</v>
+        <v>2.596899999999999</v>
       </c>
       <c r="L24" t="n">
         <v>17.6326</v>
@@ -2326,13 +2326,13 @@
         <v>13.9172</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6533</v>
+        <v>4.226</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9285</v>
+        <v>1.9284</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7251</v>
+        <v>2.2976</v>
       </c>
       <c r="V24" t="n">
         <v>-2.3659</v>
